--- a/output/laminas_comunales/comunal_i_peringrmin_a_2018_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2018_los_lagos.xlsx
@@ -699,7 +699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -708,310 +708,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ancud</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>5.95</v>
+          <t>San Pablo</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Calbuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>4</v>
+          <t>Puqueldón</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>3.82</v>
+          <t>Fresia</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chaitén</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>3.68</v>
+          <t>Llanquihue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chonchi</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>3.84</v>
+          <t>Osorno</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cochamó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>3.95</v>
+          <t>Purranque</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>3.23</v>
+          <t>Puyehue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>3.61</v>
+          <t>Cochamó</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresia</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>11.94</v>
+          <t>Ancud</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>10.23</v>
+          <t>Quellón</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>3.13</v>
+          <t>Queilén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>3.23</v>
+          <t>Chonchi</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>6.53</v>
+          <t>Puerto Montt</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>10.94</v>
+          <t>Río Negro</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maullín</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>6.59</v>
+          <t>Castro</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Osorno</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>7.1</v>
+          <t>Dalcahue</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palena</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>4.49</v>
+          <t>Quemchi</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>3.91</v>
+          <t>San Juan de la Costa</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>10.94</v>
+          <t>Calbuco</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>5.37</v>
+          <t>Chaitén</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>3.19</v>
+          <t>Los Muermos</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Purranque</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>9.279999999999999</v>
+          <t>Maullín</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Puyehue</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>9.35</v>
+          <t>Quinchao</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queilén</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>3.87</v>
+          <t>Curaco de Vélez</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quellón</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>3.28</v>
+          <t>Puerto Octay</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quemchi</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>4.48</v>
+          <t>Frutillar</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinchao</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>3.02</v>
+          <t>Puerto Varas</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>10.12</v>
+          <t>Hualaihué</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>10.29</v>
+          <t>Palena</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Pablo</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>10.66</v>
+          <t>Futaleufú</t>
+        </is>
       </c>
     </row>
   </sheetData>
